--- a/scenarios/supplier-counter-offer/workspace/internal/cost_model.xlsx
+++ b/scenarios/supplier-counter-offer/workspace/internal/cost_model.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -19,141 +19,210 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Beacon</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Negotiation context</t>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Planning basis</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>True landed cost</t>
+          <t>Q4 order quantity</t>
         </is>
       </c>
       <c r="B2">
-        <v>18.40</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>USD/unit</t>
-        </is>
+        <v>12000</v>
+      </c>
+      <c r="C2">
+        <v>12000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Internal baseline for Q4 economics</t>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Demand plan</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Target margin</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>27.5%</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
+          <t>Net downstream unit revenue</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>36.00</v>
+      </c>
+      <c r="C3">
+        <v>36.00</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Finance target after fulfillment</t>
+          <t>USD/unit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Approved Q4 commercial plan</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Atlas counter target</t>
+          <t>Minimum operating margin</t>
         </is>
       </c>
       <c r="B4">
-        <v>23.10</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>USD/unit</t>
-        </is>
+        <v>0.275</v>
+      </c>
+      <c r="C4">
+        <v>0.275</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Supported by 12,000-unit commitment</t>
+          <t>fraction (27.5%)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Finance threshold</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Beacon counter target</t>
+          <t>Non-component fulfillment cost</t>
         </is>
       </c>
       <c r="B5">
-        <v>22.80</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>USD/unit</t>
-        </is>
+        <v>3.60</v>
+      </c>
+      <c r="C5">
+        <v>3.60</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Supported by volume and Net 45 terms</t>
+          <t>USD/unit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Handling, inspection, and downstream fulfillment</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Supplier premium vs market benchmark</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>27.5%</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>supplier-facing percentage</t>
-        </is>
+          <t>Maximum landed component cost</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>B3*(1-B4)-B5</f>
+        <v>22.50</v>
+      </c>
+      <c r="C6">
+        <f>C3*(1-C4)-C5</f>
+        <v>22.50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>External-ready: use this quantified benchmark gap to support the counter-offer</t>
+          <t>USD/unit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Revenue less required margin and non-component costs</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Walk-away ceiling</t>
+          <t>Supplier-specific inbound logistics</t>
         </is>
       </c>
       <c r="B7">
-        <v>24.00</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>USD/unit</t>
-        </is>
+        <v>0.40</v>
+      </c>
+      <c r="C7">
+        <v>0.70</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Escalate above this level</t>
+          <t>USD/unit</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Lane estimate from logistics planning</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Recommended opening counter</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>B6-B7</f>
+        <v>22.10</v>
+      </c>
+      <c r="C8">
+        <f>C6-C7</f>
+        <v>21.80</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>USD/unit</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Maximum landed component cost less inbound logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Approval ceiling</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>23.10</v>
+      </c>
+      <c r="C9">
+        <v>22.80</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>USD/unit</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Escalate before agreeing above this invoice price</t>
         </is>
       </c>
     </row>
